--- a/tame_output/ON/bt/strategyON_20231021.xlsx
+++ b/tame_output/ON/bt/strategyON_20231021.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,16 +911,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.3%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.4%</t>
+          <t>130.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1375,11 +1375,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.8%</t>
+          <t>124.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1756"/>
+  <dimension ref="A1:G1757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41898,7 +41898,7 @@
         <v>45218</v>
       </c>
       <c r="B1756" t="n">
-        <v>2.892346310831684</v>
+        <v>2.890046240060276</v>
       </c>
       <c r="C1756" t="n">
         <v>2.969006534107256</v>
@@ -41914,6 +41914,29 @@
       </c>
       <c r="G1756" t="n">
         <v>4.267587128598383</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="2" t="n">
+        <v>45219</v>
+      </c>
+      <c r="B1757" t="n">
+        <v>2.900622812205591</v>
+      </c>
+      <c r="C1757" t="n">
+        <v>2.968547780644436</v>
+      </c>
+      <c r="D1757" t="n">
+        <v>1.572657441301873</v>
+      </c>
+      <c r="E1757" t="n">
+        <v>3.597254332851438</v>
+      </c>
+      <c r="F1757" t="n">
+        <v>2.164300990818542</v>
+      </c>
+      <c r="G1757" t="n">
+        <v>4.267128375135563</v>
       </c>
     </row>
   </sheetData>
